--- a/artifacts/we_detection/spot_results.xlsx
+++ b/artifacts/we_detection/spot_results.xlsx
@@ -50,12 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FDE9E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE9E7"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7">
@@ -523,7 +523,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>b1, `2, a1, _1, `3, `1, ^1, \1, ]1, Z1, Y1, U1, V1, T1, S1, S2, R1, Q1, P1, O1, N1, M1, K1, K2, J1, I1, H1, G1, F1, E1, D1, C1, B1, A2, A1</t>
+          <t>I1, H2, H1, G2, G1, F1, F3, E2, E1, D1, C1, B1, A1</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>`4, [1, X1, W1, L1, K3</t>
+          <t>J1, F2</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A3, A4, B2, B3, B4, C2, C3, C4, D2, D3, D4, E2, E3, E4, F2, F3, F4, G2, G3, G4, H2, H3, H4, I2, I3, I4, J2, J3, J4, K4, L2, L3, L4, M2, M3, M4, N2, N3, N4, O2, O3, O4, P2, P3, P4, Q2, Q3, Q4, R2, R3, R4, S3, S4, T2, T3, T4, U2, U3, U4, V2, V3, V4, W2, W3, W4, X2, X3, X4, Y2, Y3, Y4, Z2, Z3, Z4, [2, [3, [4, \2, \3, \4, ]2, ]3, ]4, ^2, ^3, ^4, _2, _3, _4, a2, a3, a4, b2, b3, b4</t>
+          <t>A2, A3, B2, B3, C2, C3, D2, D3, E3, G3, H3, I2, I3, J2, J3</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -674,34 +674,34 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>b1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>180</v>
+        <v>345</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>499</v>
+        <v>595</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>738.5</v>
+        <v>912</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.872138495623901</v>
+        <v>0.6555034058479191</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.9774983454665784</v>
+        <v>0.9249492900608519</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>18.000001</v>
+        <v>24.000001</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>0</v>
@@ -710,157 +710,161 @@
         <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>182.65</v>
+        <v>255</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="O2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>bright_defect_component</t>
+        </is>
+      </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="3" t="n">
-        <v>588</v>
+        <v>717</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>`2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>303</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>493</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>751.5</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.8676699671165066</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.9684278350515464</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="C3" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>549</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1324.5</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.7921465041254179</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.9539070939863161</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>25.500001</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>213.55</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>519</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>838.5</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.878829711593169</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.9761350407450524</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>20.000001</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="3" t="b">
+      <c r="K4" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>184.05</v>
-      </c>
-      <c r="N3" s="3" t="n">
+      <c r="L4" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>496</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1358.5</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.835374146668346</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.9665599430807542</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>25.000001</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>104.7</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="n">
-        <v>1148</v>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="n">
+        <v>679</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>`4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>514</v>
+        <v>172</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>819</v>
+        <v>1492</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.5375580644652243</v>
+        <v>0.6706981933057088</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.899505766062603</v>
+        <v>0.9307548346849657</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>30.000001</v>
+        <v>25.000001</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -869,267 +873,263 @@
         <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>dark_defect_component</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
-        <v>619</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>_1</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>372</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.78978140121176</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.9577254021698466</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>29.000001</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="C6" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>439</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>583.5</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.4559693210536193</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.8568281938325991</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>13.000001</v>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="3" t="b">
+      <c r="K6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>107.7</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="L6" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="n">
-        <v>1078</v>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="n">
+        <v>396</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>`3</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>454</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1737</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.6898337793116238</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.9366406039363709</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>24.000001</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="C7" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>434</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>818.5</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.8632699592224976</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.9709371293001187</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>18.000001</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="3" t="b">
+      <c r="K7" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="n">
-        <v>1478</v>
+      <c r="L7" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="n">
+        <v>654</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>`1</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>1744.5</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.598166140446843</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.8629730398219144</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>20.000001</v>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="C8" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>363</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1122.5</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.7881384239913338</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.9635193133047211</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>27.000001</v>
+      </c>
+      <c r="J8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="3" t="b">
+      <c r="K8" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>184.45</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="n">
-        <v>1452</v>
+      <c r="L8" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="n">
+        <v>920</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>^1</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>437</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1860.5</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.795467285474118</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0.9634904194717763</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>27.000001</v>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="C9" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>367</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1577.5</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.6904854478941432</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.922784439894706</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>31.000001</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="b">
+      <c r="K9" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="n">
-        <v>1613</v>
+      <c r="L9" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>229.5999999999999</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="n">
+        <v>1329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>\1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>514.5</v>
+        <v>1441</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.7584869899633609</v>
+        <v>0.6596706717589121</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9320652173913043</v>
+        <v>0.908288685786322</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.000001</v>
+        <v>26.000001</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0</v>
@@ -1138,157 +1138,161 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="O10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>bright_defect_component</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="n">
-        <v>377</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>]1</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>426</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>1632.5</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.8001020135736011</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.9614252061248527</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>19.000001</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="C11" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>648.5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.6796911961457007</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.9257673090649536</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>18.000001</v>
+      </c>
+      <c r="J11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="3" t="b">
+      <c r="K11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>130.4</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="n">
-        <v>1395</v>
+      <c r="L11" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>190.65</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="n">
+        <v>488</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Z1</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>414</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>804</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0.5199472137664729</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0.8088531187122736</v>
-      </c>
-      <c r="H12" s="3" t="n">
+      <c r="C12" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.8326647374048626</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.963302752293578</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>18.000001</v>
-      </c>
-      <c r="J12" s="3" t="n">
+      <c r="I12" s="4" t="n">
+        <v>27.000001</v>
+      </c>
+      <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="3" t="b">
+      <c r="K12" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>118.9</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>195.55</v>
-      </c>
-      <c r="N12" s="3" t="n">
+      <c r="L12" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>216.8999999999999</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="n">
-        <v>610</v>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="n">
+        <v>862</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>[1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>363</v>
+        <v>90</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>418</v>
+        <v>256</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1531.5</v>
+        <v>847</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.822638560454941</v>
+        <v>0.8472503633496725</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9613935969868174</v>
+        <v>0.9735632183908046</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>37.000001</v>
+        <v>22.000001</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -1297,108 +1301,104 @@
         <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>255</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
       <c r="P13" s="4" t="inlineStr"/>
       <c r="Q13" s="4" t="n">
-        <v>1307</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>419</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>374</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.8247713297727783</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.9530791788856305</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>16.000001</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="C14" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1072</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.8063267498294302</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.9614349775784753</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>20.000001</v>
+      </c>
+      <c r="J14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="b">
+      <c r="K14" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>184.65</v>
-      </c>
-      <c r="N14" s="3" t="n">
+      <c r="L14" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="N14" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="n">
-        <v>368</v>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="n">
+        <v>883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>491</v>
+        <v>308</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>371</v>
+        <v>170</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1522.5</v>
+        <v>694</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7340952430717186</v>
+        <v>0.8706556980977296</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9263766352296927</v>
+        <v>0.9699510831586303</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22.000001</v>
+        <v>20.000001</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>0</v>
@@ -1407,55 +1407,51 @@
         <v>0</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>dark_defect_component</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="4" t="inlineStr"/>
       <c r="Q15" s="4" t="n">
-        <v>1281</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>367</v>
+        <v>91</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1322</v>
+        <v>2667</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7395046514954899</v>
+        <v>0.8324281336307657</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9476702508960574</v>
+        <v>0.9633375474083439</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>25.000001</v>
+        <v>33.000001</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>0</v>
@@ -1464,1408 +1460,18 @@
         <v>0</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O16" s="4" t="inlineStr"/>
       <c r="P16" s="4" t="inlineStr"/>
       <c r="Q16" s="4" t="n">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>579</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.769247408690665</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.9530864197530864</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>12.000001</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>159.05</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1398.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.7464540704910395</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0.9500679347826086</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>22.000001</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>209</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="n">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>348</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>1160</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.8752378831611494</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.9780775716694773</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>17.000001</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>334</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>318</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>1584.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.8419620984870303</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.9646879756468798</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>29.000001</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>215.3</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>424</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>319</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>1568.5</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.8282246951679709</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.9599143206854345</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>22.000001</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="n">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>492</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>308</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>822.5</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.7975377860322446</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0.9410755148741419</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>33.000001</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="n">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>743.5</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.8923180515061596</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0.9815181518151815</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>16.000001</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>202.4</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>285</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>621.5</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.8777868534718647</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>0.9772012578616353</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>14.000001</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="n">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>850</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>0.855481389252483</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0.9692132269099202</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>16.000001</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>N1</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>416</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1092.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.7922425123056253</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.9450692041522492</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>164</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>21.000001</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="n">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>335</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>1533.5</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.8127359581381584</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0.9620451693851945</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>24.000001</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>218.5</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="n">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>463.5</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0.8152101926874001</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0.9686520376175548</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>13.000001</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>197.85</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="3" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>487</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>1835</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0.802243425496781</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0.9604815493326354</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>34.000001</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="n">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>0.7028228692818734</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0.9201520912547528</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>28.000001</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="M30" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr"/>
-      <c r="Q30" s="4" t="n">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>K2</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>224</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>994.5</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.7085089900625613</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>0.9136426274689941</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>23.000001</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="n">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>833</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.8562324922268655</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0.9708624708624709</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>16.000001</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="n">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>417</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>1172.5</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.538330555911835</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0.8665927568366593</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>18.000001</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O33" s="3" t="inlineStr"/>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="3" t="n">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>465</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0.5145229790481763</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0.7451923076923077</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>15.000001</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>147.2</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>215.9</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>486</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>1354</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.7708587522746583</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0.9442119944211994</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>156.5</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>21.000001</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>214.1499999999999</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O35" s="3" t="inlineStr"/>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="n">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1022</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.7955826164636057</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0.9476124246638851</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>14.000001</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O36" s="3" t="inlineStr"/>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="n">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>899</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.8732573219521059</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0.9771739130434782</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>21.000001</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O37" s="3" t="inlineStr"/>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="n">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>1223.5</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>0.4819494173615932</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0.8894947291893857</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>22.000001</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr"/>
-      <c r="P38" s="3" t="inlineStr"/>
-      <c r="Q38" s="3" t="n">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>832.5</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>0.8415192413260505</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>0.9557979334098737</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>19.000001</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>198.6</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O39" s="3" t="inlineStr"/>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>483</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>1681</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>0.505770836171382</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0.8896533474464144</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>22.000001</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="O40" s="3" t="inlineStr"/>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="n">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>407</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>1345</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>0.7137647473887587</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0.9314404432132964</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>22.000001</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="n">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>2522.5</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>0.7390944041078666</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0.9346054094108929</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>32.000001</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="O42" s="3" t="inlineStr"/>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="n">
-        <v>2219</v>
+        <v>2364</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2989,345 +1595,117 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>`4</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>514</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>494</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>819</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>0.5375580644652243</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.899505766062603</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>30.000001</v>
-      </c>
-      <c r="J2" s="4" t="n">
+      <c r="C2" s="3" t="n">
+        <v>345</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>595</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>912</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.6555034058479191</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.9249492900608519</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>24.000001</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="4" t="b">
+      <c r="K2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="N2" s="4" t="n">
+      <c r="L2" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="N2" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>dark_defect_component</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="n">
-        <v>619</v>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>bright_defect_component</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="n">
+        <v>717</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>[1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>363</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>418</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>1531.5</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.822638560454941</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.9613935969868174</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>37.000001</v>
-      </c>
-      <c r="J3" s="4" t="n">
+      <c r="C3" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1441</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.6596706717589121</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.908288685786322</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>26.000001</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="b">
+      <c r="K3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L3" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="L3" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>bright_defect_component</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="n">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>491</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1522.5</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0.7340952430717186</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0.9263766352296927</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>22.000001</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>206</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>dark_defect_component</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="n">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>203</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>367</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.7395046514954899</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0.9476702508960574</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>25.000001</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="n">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>487</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>236</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1835</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0.802243425496781</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0.9604815493326354</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>34.000001</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="n">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1089</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.7028228692818734</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.9201520912547528</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>28.000001</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>255</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>bright_defect_component</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="n">
-        <v>888</v>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="n">
+        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -3341,13 +1719,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3379,13 +1757,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.75020015882688</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3395,13 +1773,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.5</v>
+        <v>267.5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6380493753606353</v>
+        <v>0.2184734768493648</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>0.6128293241695304</v>
       </c>
     </row>
     <row r="4">
@@ -3411,10 +1789,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8085181381420814</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -3427,13 +1805,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7798381254407765</v>
+        <v>0.4581569667695897</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -3443,13 +1821,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6380493753606353</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3459,13 +1837,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.249003426629153</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.4943253467843632</v>
       </c>
     </row>
     <row r="8">
@@ -3475,10 +1853,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8061450660379307</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -3487,17 +1865,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>circularity</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1521</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>0.145815913667232</v>
+        <v>0.7429559153356595</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6410958904109589</v>
+        <v>0.9629629629629629</v>
       </c>
     </row>
     <row r="10">
@@ -3507,13 +1885,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2709866035849536</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5402061855670103</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3523,10 +1901,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7539822368615503</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -3539,10 +1917,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>14.5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.8982491906543908</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -3555,13 +1933,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.5098843347951539</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="14">
@@ -3571,7 +1949,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>0.7853981633974483</v>
@@ -3587,61 +1965,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3817974723079914</v>
+        <v>0.8983534868245348</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>circularity</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>703.5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.3398007061118062</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.7994318181818182</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>circularity</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>1217.5</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2976984757249524</v>
+        <v>0.06715185704657405</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5154639175257731</v>
+        <v>0.4260717410323709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>circularity</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.5</v>
+        <v>824</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.1940582522956963</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.7363717605004468</v>
       </c>
     </row>
     <row r="19">
@@ -3651,13 +2029,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>241</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.1915486974759165</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.5015608740894901</v>
       </c>
     </row>
     <row r="20">
@@ -3667,10 +2045,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.8803370121606843</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -3683,13 +2061,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.293445670720228</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -3699,13 +2077,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.2850452427726601</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.5196850393700787</v>
       </c>
     </row>
     <row r="23">
@@ -3715,13 +2093,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.7648265021927309</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0.9069767441860465</v>
       </c>
     </row>
     <row r="24">
@@ -3731,10 +2109,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7689393938672696</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -3747,13 +2125,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.7126537717491254</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="26">
@@ -3763,13 +2141,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4646116503384779</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D26" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3779,10 +2157,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5890486225480862</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -3795,29 +2173,29 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6430287075658971</v>
+        <v>0.75020015882688</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>circularity</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.5</v>
+        <v>1084</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.08724560683537384</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.3177953679272941</v>
       </c>
     </row>
     <row r="30">
@@ -3827,10 +2205,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -3859,13 +2237,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.3252234356020246</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="33">
@@ -3875,10 +2253,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -3891,13 +2269,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.5239942929246549</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="35">
@@ -3907,13 +2285,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6935989106655485</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8823529411764706</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3923,10 +2301,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
@@ -3939,10 +2317,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8573716100878628</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -3955,13 +2333,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12.5</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6915631487216456</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9259259259259259</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3971,13 +2349,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2832016129060749</v>
+        <v>0.4227904662826321</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="40">
@@ -3987,13 +2365,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>109.5</v>
+        <v>3.5</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8437011268446083</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9563318777292577</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -4003,13 +2381,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8061450660379307</v>
+        <v>0.2698969480075393</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0.5192307692307693</v>
       </c>
     </row>
     <row r="42">
@@ -4035,13 +2413,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5.5</v>
+        <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7798381254407765</v>
+        <v>0.2994537072597861</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0.5569620253164557</v>
       </c>
     </row>
     <row r="44">
@@ -4051,13 +2429,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20.5</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6505484175370557</v>
+        <v>0.75020015882688</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8913043478260869</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4083,13 +2461,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6288121515433458</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8823529411764706</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4099,10 +2477,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8852008380317046</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -4115,13 +2493,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>74</v>
+        <v>3.5</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8379066289367699</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4131,13 +2509,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27.5</v>
+        <v>15</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5151811657273628</v>
+        <v>0.4878351534030369</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7236842105263158</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
@@ -4147,7 +2525,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
         <v>0.7853981633974483</v>
@@ -4163,13 +2541,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.5237700925094588</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0.8823529411764706</v>
       </c>
     </row>
     <row r="52">
@@ -4179,13 +2557,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6449160528303446</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4195,10 +2573,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8198545354117053</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
@@ -4211,13 +2589,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8573716100878628</v>
+        <v>0.419103336856013</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0.6470588235294118</v>
       </c>
     </row>
     <row r="55">
@@ -4227,13 +2605,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.3054379778463931</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="56">
@@ -4243,13 +2621,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23.5</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.745750624981503</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9038461538461539</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -4259,13 +2637,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6587925570046588</v>
+        <v>0.3572381708699428</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="58">
@@ -4275,13 +2653,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.5548791279733458</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="59">
@@ -4291,10 +2669,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
@@ -4323,13 +2701,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>55.5</v>
+        <v>19</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4650016144919348</v>
+        <v>0.4266281227487519</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8538461538461538</v>
+        <v>0.7169811320754716</v>
       </c>
     </row>
     <row r="62">
@@ -4339,13 +2717,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6430287075658971</v>
+        <v>0.7798381254407765</v>
       </c>
       <c r="D62" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4355,10 +2733,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
@@ -4371,10 +2749,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
@@ -4387,13 +2765,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.2418435198113792</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66">
@@ -4403,13 +2781,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>50.5</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.3345016819016026</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0.6352201257861635</v>
       </c>
     </row>
     <row r="67">
@@ -4419,13 +2797,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.5304941111487503</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="68">
@@ -4435,13 +2813,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6380493753606353</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4451,10 +2829,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.7798381254407765</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
@@ -4467,13 +2845,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7186827894596279</v>
+        <v>0.2632799351918042</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.6181818181818182</v>
       </c>
     </row>
     <row r="71">
@@ -4483,10 +2861,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.8031141418478369</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
@@ -4499,13 +2877,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.3479695585322395</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0.5957446808510638</v>
       </c>
     </row>
     <row r="73">
@@ -4515,10 +2893,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6634421171786479</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
@@ -4527,17 +2905,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>circularity</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>709</v>
+        <v>19</v>
       </c>
       <c r="C74" t="n">
-        <v>0.337954105004622</v>
+        <v>0.2569112093172837</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7431865828092243</v>
+        <v>0.5428571428571428</v>
       </c>
     </row>
     <row r="75">
@@ -4547,10 +2925,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.8085181381420814</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -4563,13 +2941,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>28</v>
+        <v>3.5</v>
       </c>
       <c r="C76" t="n">
-        <v>0.75020015882688</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9180327868852459</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4579,13 +2957,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>43.5</v>
+        <v>12.5</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7651890443307279</v>
+        <v>0.5953969514499048</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.8064516129032258</v>
       </c>
     </row>
     <row r="78">
@@ -4595,13 +2973,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4836870396227584</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D78" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4611,10 +2989,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.778573021914597</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -4627,13 +3005,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3215143537829486</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5853658536585366</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4643,7 +3021,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C81" t="n">
         <v>0.7853981633974483</v>
@@ -4659,10 +3037,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.8061450660379307</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -4691,13 +3069,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>86</v>
+        <v>6.5</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4027779985881532</v>
+        <v>0.778573021914597</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7107438016528925</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="85">
@@ -4723,10 +3101,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.9432711667053002</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
@@ -4739,13 +3117,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>26.5</v>
+        <v>8.5</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4035035065229647</v>
+        <v>0.5936061048440535</v>
       </c>
       <c r="D87" t="n">
-        <v>0.726027397260274</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="88">
@@ -4755,10 +3133,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5890486225480862</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -4771,13 +3149,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>303.5</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8836043777530204</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9774557165861514</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4803,13 +3181,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3368825575592005</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D91" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4819,13 +3197,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="C92" t="n">
-        <v>0.8061450660379307</v>
+        <v>0.3937031346223153</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="93">
@@ -4835,13 +3213,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8085181381420813</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9818181818181818</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4867,13 +3245,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7207940855310676</v>
+        <v>0.7429559153356595</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8923076923076924</v>
+        <v>0.9629629629629629</v>
       </c>
     </row>
     <row r="96">
@@ -4883,13 +3261,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>117.5</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3639062674011274</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D96" t="n">
-        <v>0.6368563685636857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4899,13 +3277,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>26.5</v>
+        <v>5</v>
       </c>
       <c r="C97" t="n">
-        <v>0.4661496393794287</v>
+        <v>0.2857522751290998</v>
       </c>
       <c r="D97" t="n">
-        <v>0.828125</v>
+        <v>0.5263157894736842</v>
       </c>
     </row>
     <row r="98">
@@ -4915,13 +3293,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.7964953919549047</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="99">
@@ -4931,13 +3309,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6430287075658971</v>
+        <v>0.8085181381420814</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9230769230769231</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -4947,13 +3325,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25</v>
+        <v>3.5</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7486279144000415</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9259259259259259</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -4963,13 +3341,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>407.5</v>
+        <v>14</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7736871205894115</v>
+        <v>0.7176767785380505</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9509918319719953</v>
+        <v>0.9655172413793104</v>
       </c>
     </row>
     <row r="102">
@@ -4979,10 +3357,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8983534868245348</v>
+        <v>0.6737651190752144</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -4995,10 +3373,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>0.778573021914597</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
@@ -5011,10 +3389,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -5027,10 +3405,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -5043,13 +3421,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6269475859030688</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -5059,13 +3437,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.2290784833847948</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="108">
@@ -5075,10 +3453,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
@@ -5091,10 +3469,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>0.8061450660379307</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -5107,10 +3485,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="C110" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -5139,10 +3517,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -5155,29 +3533,29 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>444</v>
+        <v>2</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8379807238781141</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9579288025889967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>circularity</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1179</v>
+        <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3407777911158569</v>
+        <v>0.6430287075658971</v>
       </c>
       <c r="D114" t="n">
-        <v>0.6982528871779686</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="115">
@@ -5187,13 +3565,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>37.5</v>
+        <v>7</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2840904472537101</v>
+        <v>0.9432711667053002</v>
       </c>
       <c r="D115" t="n">
-        <v>0.5319148936170213</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5203,13 +3581,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="C116" t="n">
-        <v>0.6449160528303446</v>
+        <v>0.8982491906543908</v>
       </c>
       <c r="D116" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -5235,13 +3613,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>114.5</v>
+        <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1870816436692324</v>
+        <v>0.6449160528303446</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4386973180076628</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="119">
@@ -5251,10 +3629,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="C119" t="n">
-        <v>0.8983534868245348</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
@@ -5267,10 +3645,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="C120" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.8198545354117053</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -5283,10 +3661,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C121" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -5299,13 +3677,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>39.5</v>
+        <v>3.5</v>
       </c>
       <c r="C122" t="n">
-        <v>0.6376968654675641</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D122" t="n">
-        <v>0.8586956521739131</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -5315,13 +3693,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="C123" t="n">
-        <v>0.7964953919549047</v>
+        <v>0.8061450660379307</v>
       </c>
       <c r="D123" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -5331,10 +3709,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
@@ -5347,13 +3725,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="C125" t="n">
-        <v>0.223694718571203</v>
+        <v>0.6915631487216456</v>
       </c>
       <c r="D125" t="n">
-        <v>0.45</v>
+        <v>0.9615384615384616</v>
       </c>
     </row>
     <row r="126">
@@ -5363,10 +3741,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>0.7539822368615503</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -5379,13 +3757,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0.6162358447506514</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D127" t="n">
-        <v>0.8846153846153846</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -5395,10 +3773,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C128" t="n">
-        <v>0.8061450660379307</v>
+        <v>0.8085181381420814</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -5411,13 +3789,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0.3936640336287403</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D129" t="n">
-        <v>0.8260869565217391</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -5427,13 +3805,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6251822815242696</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D130" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -5443,10 +3821,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="C131" t="n">
-        <v>0.8031141418478369</v>
+        <v>0.3436116964863836</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -5455,17 +3833,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>circularity</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2511.5</v>
+        <v>5</v>
       </c>
       <c r="C132" t="n">
-        <v>0.03457376440844661</v>
+        <v>0.2218670546916489</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4804859383967859</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="133">
@@ -5475,13 +3853,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>164</v>
+        <v>6.5</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2394654126253825</v>
+        <v>0.778573021914597</v>
       </c>
       <c r="D133" t="n">
-        <v>0.5942028985507246</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -5491,13 +3869,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>392.5</v>
+        <v>18.5</v>
       </c>
       <c r="C134" t="n">
-        <v>0.8607462915881956</v>
+        <v>0.4070091307654015</v>
       </c>
       <c r="D134" t="n">
-        <v>0.9703337453646477</v>
+        <v>0.6727272727272727</v>
       </c>
     </row>
     <row r="135">
@@ -5507,13 +3885,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C135" t="n">
-        <v>0.555856219972681</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D135" t="n">
-        <v>0.8048780487804879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -5523,13 +3901,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>27</v>
+        <v>3.5</v>
       </c>
       <c r="C136" t="n">
-        <v>0.6710841485978906</v>
+        <v>0.8001063703614795</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8852459016393442</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -5539,10 +3917,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C137" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.8085181381420814</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
@@ -5555,13 +3933,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="C138" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.3659368753012543</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0.6326530612244898</v>
       </c>
     </row>
     <row r="139">
@@ -5571,29 +3949,29 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>19.5</v>
+        <v>3</v>
       </c>
       <c r="C139" t="n">
-        <v>0.5980123401348733</v>
+        <v>0.5890486225480862</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>circularity</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2</v>
+        <v>1151</v>
       </c>
       <c r="C140" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.1240805839467925</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0.6277611126261249</v>
       </c>
     </row>
     <row r="141">
@@ -5603,10 +3981,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="C141" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.8061450660379307</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -5619,10 +3997,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.8085181381420814</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -5635,29 +4013,29 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>51.5</v>
+        <v>17.5</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3602444602008608</v>
+        <v>0.6863827608712632</v>
       </c>
       <c r="D143" t="n">
-        <v>0.6821192052980133</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>circularity</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1296.5</v>
+        <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4130279217167571</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D144" t="n">
-        <v>0.8239593263425484</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -5667,13 +4045,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3323494804305461</v>
+        <v>0.7411416266302412</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6267029972752044</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -5683,13 +4061,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="C146" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.778573021914597</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="147">
@@ -5699,10 +4077,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D147" t="n">
         <v>1</v>
@@ -5715,10 +4093,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C148" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D148" t="n">
         <v>1</v>
@@ -5731,13 +4109,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>89.5</v>
+        <v>4</v>
       </c>
       <c r="C149" t="n">
-        <v>0.2701165206105955</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -5747,13 +4125,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>15.5</v>
+        <v>2</v>
       </c>
       <c r="C150" t="n">
-        <v>0.475343142158489</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D150" t="n">
-        <v>0.7948717948717948</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -5763,13 +4141,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>25.5</v>
+        <v>3</v>
       </c>
       <c r="C151" t="n">
-        <v>0.43725952114481</v>
+        <v>0.8085181381420814</v>
       </c>
       <c r="D151" t="n">
-        <v>0.6710526315789473</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -5779,10 +4157,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.8001063703614795</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
@@ -5795,13 +4173,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>7.5</v>
+        <v>28.5</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8983534868245348</v>
+        <v>0.533915021384296</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0.7702702702702703</v>
       </c>
     </row>
     <row r="154">
@@ -5811,13 +4189,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C154" t="n">
-        <v>0.6981317007977318</v>
+        <v>0.3892865109572985</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0.7027027027027027</v>
       </c>
     </row>
     <row r="155">
@@ -5827,13 +4205,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.353096875114315</v>
+        <v>0.7853981633974483</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6606334841628959</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -5843,13 +4221,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C156" t="n">
-        <v>0.7154915583244541</v>
+        <v>0.4836870396227584</v>
       </c>
       <c r="D156" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="157">
@@ -5859,13 +4237,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C157" t="n">
-        <v>0.2286018201032798</v>
+        <v>0.6981317007977318</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -5875,10 +4253,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C158" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.6737651190752144</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
@@ -5891,45 +4269,2541 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C159" t="n">
-        <v>0.7853981633974483</v>
+        <v>0.4918780677141811</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0.8378378378378378</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>circularity</t>
+          <t>area</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>10732</v>
+        <v>22.5</v>
       </c>
       <c r="C160" t="n">
-        <v>0.01270709377883704</v>
+        <v>0.2460401204406521</v>
       </c>
       <c r="D160" t="n">
-        <v>0.04605465020222935</v>
+        <v>0.4736842105263158</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>4</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.6449160528303446</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>2</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.50013343921792</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>18</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.8323186927986581</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.5890486225480862</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.552648881783745</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.8428571428571429</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>4</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>12</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.8085181381420814</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>3</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.8085181381420814</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>9</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.6872354501543845</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.7234010606573869</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>2</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.5487856891751663</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.8291139240506329</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>5</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.8061450660379307</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>7</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.75020015882688</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>9</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.6872354501543845</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>2</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>4</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.261974658637958</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.6380493753606353</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>5</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.8061450660379307</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.2454413978519316</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.5516314364833987</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.5449705313375665</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>4</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.3054379778463931</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.8983534868245348</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>136</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.1856688980239031</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.7798381254407765</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>10</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.641141357875468</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>10</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.7635949446159828</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.4802251895170941</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.7286432160804021</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>6</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.7539822368615503</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.7798381254407765</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>34</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.6090873832286589</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.8607594936708861</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>5</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.8061450660379307</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.6087338431623827</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.8658536585365854</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.778573021914597</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>7</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.75020015882688</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.6046414240632183</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.8536585365853658</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>86</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.2485396078579013</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.5029239766081871</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>14</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.7176767676094516</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.9032258064516129</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.7798381254407765</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>4</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.2974334651254719</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.5590551181102362</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.6660833978322632</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.9034090909090909</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.7126537717491254</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.5475231182850783</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>4</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
           <t>circularity</t>
         </is>
       </c>
-      <c r="B161" t="n">
-        <v>2128</v>
-      </c>
-      <c r="C161" t="n">
-        <v>0.07127233952074963</v>
-      </c>
-      <c r="D161" t="n">
-        <v>0.3953185955786736</v>
+      <c r="B240" t="n">
+        <v>4255</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.03880322606804962</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.3049086348978861</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>7</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.75020015882688</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>circularity</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.3666719732843372</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.8075407990996061</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>11</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.4045297167920514</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.2001216217867647</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.4565972222222222</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.7798381254407765</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>5</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.8061450660379307</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>51</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.440524466103202</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.7338129496402878</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.7382922197978818</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>97</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.3867263320622064</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.8584070796460177</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>17</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.8714646463829057</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.50013343921792</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>3</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.2290784833847948</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>5</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.8061450660379307</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>12</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.8085181381420814</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>13</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.5239942929246549</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.8726869015740993</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.9821428571428571</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>2</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>23</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.6662308698336755</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>7</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.75020015882688</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>4</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>4</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.6449160528303446</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>2</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>4</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.6449160528303446</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.7798381254407765</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>66</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.7473221285111732</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>1</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.1977708565068531</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.6186511240632806</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>3</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.8085181381420814</v>
+      </c>
+      <c r="D282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.8803370121606843</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>254</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.3327464301916872</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.635</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>14</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>2</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>circularity</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2370</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.04457994768312138</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.4205856255545696</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>4</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.6915631377813787</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.4958911247271433</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>16</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.8202020201250876</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.325487728747256</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.575</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>19</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.1612033771967075</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.3877551020408163</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.5953969514499048</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.4670041325504108</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.7674418604651163</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.4698206131983093</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.7121212121212122</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>7</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.75020015882688</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>2</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.8001063703614795</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.7798381254407765</v>
+      </c>
+      <c r="D307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.3190071565458553</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.6170212765957447</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>5</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.8061450660379307</v>
+      </c>
+      <c r="D310" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.3558192250744366</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.639344262295082</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.7853981633974483</v>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>2</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.6981317007977318</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.6286796396289692</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>circularity</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>10057.5</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.0641484388792187</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.4504938299254216</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>86</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.5152245247266415</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.8037383177570093</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>circularity</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>8941</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.01508571446984226</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.1265167219702705</v>
       </c>
     </row>
   </sheetData>
